--- a/data/trans_camb/P19C02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 1,04</t>
+          <t>-16,47; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -0,19</t>
+          <t>-18,75; -0,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 25,32</t>
+          <t>6,22; 24,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 0,41</t>
+          <t>-17,77; 0,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,21; -0,91</t>
+          <t>-16,86; -0,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 19,31</t>
+          <t>1,5; 18,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -1,53</t>
+          <t>-15,35; -2,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -3,33</t>
+          <t>-15,36; -2,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 19,91</t>
+          <t>6,89; 19,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 4,7</t>
+          <t>-44,48; 5,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,76; -0,95</t>
+          <t>-49,68; -2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,53; 89,65</t>
+          <t>16,66; 89,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 1,38</t>
+          <t>-44,99; 0,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,38; -2,58</t>
+          <t>-43,59; -2,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 65,13</t>
+          <t>4,72; 65,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,45; -4,82</t>
+          <t>-40,26; -7,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,19; -10,63</t>
+          <t>-41,17; -9,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 66,69</t>
+          <t>17,79; 65,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 3,84</t>
+          <t>-8,87; 4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 8,94</t>
+          <t>-3,87; 8,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 19,32</t>
+          <t>4,35; 19,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 7,93</t>
+          <t>-4,02; 7,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 13,12</t>
+          <t>0,06; 12,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 14,07</t>
+          <t>3,17; 15,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,2</t>
+          <t>-4,56; 3,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 10,33</t>
+          <t>0,13; 9,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 15,26</t>
+          <t>5,65; 14,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 16,78</t>
+          <t>-31,06; 16,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 39,31</t>
+          <t>-14,24; 37,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 85,13</t>
+          <t>14,68; 81,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 33,01</t>
+          <t>-14,24; 34,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 54,24</t>
+          <t>-0,28; 53,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 59,33</t>
+          <t>10,81; 64,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 17,97</t>
+          <t>-15,87; 16,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 43,22</t>
+          <t>0,32; 39,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 62,46</t>
+          <t>19,77; 60,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 2,41</t>
+          <t>-13,64; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -0,0</t>
+          <t>-15,0; 0,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 0,34</t>
+          <t>-14,55; 0,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 11,99</t>
+          <t>-3,0; 11,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,37</t>
+          <t>-7,14; 5,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,88</t>
+          <t>-5,03; 7,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 4,08</t>
+          <t>-5,81; 4,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,92</t>
+          <t>-9,66; 1,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 2,2</t>
+          <t>-8,15; 2,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 9,86</t>
+          <t>-39,7; 5,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,21; 1,34</t>
+          <t>-44,04; 0,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 1,41</t>
+          <t>-41,59; 2,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 52,61</t>
+          <t>-10,13; 51,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 29,47</t>
+          <t>-24,43; 28,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 37,05</t>
+          <t>-17,21; 34,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 15,95</t>
+          <t>-18,98; 18,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 3,84</t>
+          <t>-31,62; 5,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 8,56</t>
+          <t>-25,66; 9,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,08</t>
+          <t>-8,06; 7,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 2,96</t>
+          <t>-12,2; 2,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,24; 29,19</t>
+          <t>11,54; 29,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 8,89</t>
+          <t>-5,97; 8,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 3,29</t>
+          <t>-11,31; 2,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 18,93</t>
+          <t>-8,05; 19,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,96</t>
+          <t>-4,35; 5,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 1,3</t>
+          <t>-8,88; 1,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 20,68</t>
+          <t>3,02; 20,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 27,57</t>
+          <t>-23,24; 29,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 12,1</t>
+          <t>-36,59; 10,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,5; 115,77</t>
+          <t>32,75; 112,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 35,63</t>
+          <t>-18,2; 33,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 13,37</t>
+          <t>-34,91; 10,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 70,71</t>
+          <t>-23,62; 72,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 22,29</t>
+          <t>-13,91; 22,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 4,71</t>
+          <t>-27,79; 4,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 75,81</t>
+          <t>11,11; 76,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 10,29</t>
+          <t>-6,16; 11,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,77; 56,89</t>
+          <t>36,16; 57,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58,69; 73,09</t>
+          <t>58,96; 73,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 13,02</t>
+          <t>-5,08; 13,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,17; 54,62</t>
+          <t>34,89; 54,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,92; 70,31</t>
+          <t>55,99; 70,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,12</t>
+          <t>-3,75; 9,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39,26; 52,73</t>
+          <t>38,64; 52,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59,83; 70,07</t>
+          <t>60,02; 70,05</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 63,65</t>
+          <t>-26,28; 73,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>137,18; 359,31</t>
+          <t>142,11; 365,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221,33; 506,32</t>
+          <t>221,96; 471,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 68,18</t>
+          <t>-17,98; 64,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>117,71; 291,84</t>
+          <t>110,76; 279,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>181,11; 375,09</t>
+          <t>184,26; 408,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 48,43</t>
+          <t>-14,01; 49,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>144,78; 278,17</t>
+          <t>143,32; 277,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>224,91; 374,11</t>
+          <t>221,28; 384,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 4,48</t>
+          <t>-13,48; 4,82</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,64; -4,1</t>
+          <t>-21,08; -3,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,98; -9,6</t>
+          <t>-25,83; -9,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 1,83</t>
+          <t>-14,94; 1,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 7,46</t>
+          <t>-11,13; 7,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -5,92</t>
+          <t>-20,83; -5,2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 0,88</t>
+          <t>-12,08; 0,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -0,22</t>
+          <t>-13,11; -0,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -9,42</t>
+          <t>-21,06; -9,45</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 14,64</t>
+          <t>-34,04; 16,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,68; -12,52</t>
+          <t>-52,53; -10,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,76; -31,13</t>
+          <t>-63,11; -29,25</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 6,67</t>
+          <t>-39,59; 6,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 25,74</t>
+          <t>-29,35; 25,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,17; -20,81</t>
+          <t>-54,46; -18,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 2,5</t>
+          <t>-31,29; 0,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,51; -1,24</t>
+          <t>-35,28; -2,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,31; -31,46</t>
+          <t>-56,19; -31,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,47</t>
+          <t>-4,3; 6,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,12</t>
+          <t>-0,55; 12,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13,58; 26,48</t>
+          <t>14,58; 27,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,19</t>
+          <t>0,34; 11,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,7</t>
+          <t>3,16; 14,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,85; 58,02</t>
+          <t>19,23; 57,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,59</t>
+          <t>-0,21; 8,02</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,17</t>
+          <t>3,09; 11,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19,29; 46,72</t>
+          <t>19,47; 46,87</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 28,16</t>
+          <t>-14,4; 29,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,07; 51,5</t>
+          <t>-1,99; 53,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45,56; 113,07</t>
+          <t>49,15; 116,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,08; 53,99</t>
+          <t>1,44; 52,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,65; 63,12</t>
+          <t>11,97; 68,4</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>71,42; 247,41</t>
+          <t>72,8; 257,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,31; 32,08</t>
+          <t>-0,76; 32,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>10,69; 46,71</t>
+          <t>11,19; 47,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72,12; 190,79</t>
+          <t>71,98; 188,83</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,14; 17,52</t>
+          <t>6,64; 17,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17,14; 28,47</t>
+          <t>17,59; 28,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 35,01</t>
+          <t>-8,8; 34,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 9,28</t>
+          <t>-1,31; 9,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,62; 23,67</t>
+          <t>12,23; 23,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>29,93; 40,05</t>
+          <t>30,15; 39,56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,28; 11,4</t>
+          <t>3,76; 11,54</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>16,28; 24,05</t>
+          <t>16,56; 24,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 35,14</t>
+          <t>3,31; 35,15</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>18,36; 64,33</t>
+          <t>20,2; 65,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>50,41; 107,66</t>
+          <t>53,04; 105,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 120,89</t>
+          <t>-27,52; 119,95</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 29,98</t>
+          <t>-3,58; 29,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>34,37; 76,08</t>
+          <t>33,4; 74,87</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>79,38; 131,04</t>
+          <t>81,12; 128,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,25; 37,64</t>
+          <t>10,89; 39,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>46,87; 80,26</t>
+          <t>47,93; 82,65</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 111,54</t>
+          <t>10,19; 112,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,66</t>
+          <t>-1,25; 3,78</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,79</t>
+          <t>3,42; 8,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,72; 19,28</t>
+          <t>5,34; 19,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,61</t>
+          <t>-0,6; 4,48</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,66</t>
+          <t>5,33; 10,55</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,34; 30,13</t>
+          <t>16,6; 29,82</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,22</t>
+          <t>-0,24; 3,34</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,92</t>
+          <t>5,53; 9,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12,9; 22,36</t>
+          <t>12,78; 22,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,47</t>
+          <t>-4,28; 13,91</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11,52; 32,0</t>
+          <t>11,37; 31,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>20,64; 69,24</t>
+          <t>19,64; 68,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 16,85</t>
+          <t>-2,01; 16,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>18,18; 38,44</t>
+          <t>17,51; 38,09</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>54,66; 105,87</t>
+          <t>55,69; 103,71</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,66</t>
+          <t>-0,71; 12,05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>17,38; 31,98</t>
+          <t>18,32; 32,88</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>44,04; 79,34</t>
+          <t>43,93; 79,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,74</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,52</t>
+          <t>12,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>13,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 1,17</t>
+          <t>-15,95; 1,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -0,76</t>
+          <t>-17,7; -0,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 24,29</t>
+          <t>5,2; 23,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 0,26</t>
+          <t>-18,07; -0,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -0,93</t>
+          <t>-17,54; 0,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 18,84</t>
+          <t>4,48; 21,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -2,22</t>
+          <t>-15,21; -1,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -2,88</t>
+          <t>-14,99; -2,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 19,82</t>
+          <t>7,54; 20,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 5,0</t>
+          <t>-42,85; 4,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,68; -2,54</t>
+          <t>-47,77; -0,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 89,61</t>
+          <t>12,79; 84,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 0,94</t>
+          <t>-45,09; 0,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,59; -2,27</t>
+          <t>-45,36; 2,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 65,55</t>
+          <t>10,47; 71,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,26; -7,01</t>
+          <t>-40,4; -5,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,17; -9,4</t>
+          <t>-40,32; -7,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 65,9</t>
+          <t>20,25; 67,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,3</t>
+          <t>9,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 4,0</t>
+          <t>-9,15; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 8,71</t>
+          <t>-4,31; 9,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 19,07</t>
+          <t>3,72; 18,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 7,99</t>
+          <t>-4,86; 7,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 12,95</t>
+          <t>0,73; 13,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 15,0</t>
+          <t>2,71; 14,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,98</t>
+          <t>-4,88; 3,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 9,54</t>
+          <t>0,04; 9,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 14,79</t>
+          <t>5,42; 14,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 16,98</t>
+          <t>-31,31; 16,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 37,71</t>
+          <t>-14,68; 41,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 81,24</t>
+          <t>13,94; 80,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 34,09</t>
+          <t>-16,29; 32,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 53,98</t>
+          <t>2,26; 55,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 64,62</t>
+          <t>8,58; 60,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 16,93</t>
+          <t>-17,0; 13,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 39,02</t>
+          <t>0,28; 40,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 60,46</t>
+          <t>18,74; 57,92</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-2,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 1,52</t>
+          <t>-14,02; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 0,04</t>
+          <t>-15,32; -0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 0,38</t>
+          <t>-15,42; -0,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 11,9</t>
+          <t>-3,19; 11,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 5,92</t>
+          <t>-7,68; 6,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,69</t>
+          <t>-5,52; 7,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 4,58</t>
+          <t>-5,3; 5,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 1,5</t>
+          <t>-9,69; 1,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,45</t>
+          <t>-8,38; 2,06</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-22,59%</t>
+          <t>-23,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-10,56%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 5,97</t>
+          <t>-40,89; 5,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 0,01</t>
+          <t>-43,52; 0,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 2,09</t>
+          <t>-43,47; -1,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 51,61</t>
+          <t>-11,39; 52,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 28,35</t>
+          <t>-25,65; 29,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 34,74</t>
+          <t>-18,8; 34,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 18,58</t>
+          <t>-17,74; 19,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 5,65</t>
+          <t>-30,71; 4,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 9,58</t>
+          <t>-27,46; 7,89</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,58</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,47</t>
+          <t>18,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,19</t>
+          <t>19,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 7,41</t>
+          <t>-8,5; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 2,7</t>
+          <t>-11,91; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,54; 29,68</t>
+          <t>10,91; 29,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 8,22</t>
+          <t>-5,73; 8,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 2,86</t>
+          <t>-10,87; 3,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 19,31</t>
+          <t>11,48; 24,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 5,97</t>
+          <t>-4,84; 5,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 1,23</t>
+          <t>-9,01; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 20,99</t>
+          <t>13,78; 24,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 29,25</t>
+          <t>-24,44; 27,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 10,89</t>
+          <t>-34,67; 10,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,75; 112,67</t>
+          <t>32,34; 109,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 33,55</t>
+          <t>-17,44; 31,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 10,65</t>
+          <t>-33,64; 12,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 72,0</t>
+          <t>34,19; 101,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 22,56</t>
+          <t>-15,51; 21,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 4,87</t>
+          <t>-28,58; 3,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,11; 76,05</t>
+          <t>42,79; 93,83</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66,44</t>
+          <t>64,98</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,9</t>
+          <t>63,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>65,2</t>
+          <t>64,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 11,31</t>
+          <t>-5,93; 11,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,16; 57,32</t>
+          <t>36,42; 56,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58,96; 73,33</t>
+          <t>57,95; 71,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 13,16</t>
+          <t>-4,07; 13,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,89; 54,53</t>
+          <t>34,98; 54,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,99; 70,91</t>
+          <t>56,64; 70,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 9,21</t>
+          <t>-2,6; 9,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,64; 52,83</t>
+          <t>38,28; 52,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60,02; 70,05</t>
+          <t>59,34; 69,61</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>322,07%</t>
+          <t>314,99%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>264,81%</t>
+          <t>264,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>291,08%</t>
+          <t>287,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 73,11</t>
+          <t>-24,61; 68,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>142,11; 365,48</t>
+          <t>139,44; 345,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221,96; 471,4</t>
+          <t>220,05; 472,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 64,63</t>
+          <t>-14,7; 74,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>110,76; 279,49</t>
+          <t>116,92; 291,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>184,26; 408,17</t>
+          <t>180,76; 382,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 49,11</t>
+          <t>-9,91; 52,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>143,32; 277,96</t>
+          <t>149,34; 282,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>221,28; 384,96</t>
+          <t>218,32; 375,36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-17,4</t>
+          <t>-17,79</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-12,86</t>
+          <t>-13,14</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-15,1</t>
+          <t>-15,42</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 4,82</t>
+          <t>-14,3; 4,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -3,15</t>
+          <t>-21,55; -3,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -9,03</t>
+          <t>-25,77; -9,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 1,88</t>
+          <t>-14,72; 1,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 7,19</t>
+          <t>-10,16; 7,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -5,2</t>
+          <t>-22,47; -6,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 0,12</t>
+          <t>-11,94; 0,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,11; -0,94</t>
+          <t>-12,58; -0,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-21,06; -9,45</t>
+          <t>-21,03; -9,53</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-49,08%</t>
+          <t>-50,21%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-38,94%</t>
+          <t>-39,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-44,16%</t>
+          <t>-45,09%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 16,0</t>
+          <t>-35,91; 14,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,53; -10,1</t>
+          <t>-52,34; -10,5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,11; -29,25</t>
+          <t>-64,48; -32,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 6,46</t>
+          <t>-39,74; 7,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 25,38</t>
+          <t>-27,15; 25,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,46; -18,56</t>
+          <t>-55,6; -20,17</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 0,65</t>
+          <t>-30,92; 1,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -2,75</t>
+          <t>-34,07; -2,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-56,19; -31,21</t>
+          <t>-55,68; -31,59</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,69</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,13</t>
+          <t>19,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28,44</t>
+          <t>19,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,73</t>
+          <t>-4,48; 7,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 12,57</t>
+          <t>-0,51; 11,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14,58; 27,42</t>
+          <t>13,73; 25,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 11,68</t>
+          <t>1,25; 12,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,16; 14,77</t>
+          <t>2,93; 14,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,23; 57,2</t>
+          <t>15,08; 25,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 8,02</t>
+          <t>-0,07; 8,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,09; 11,4</t>
+          <t>3,15; 11,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19,47; 46,87</t>
+          <t>15,82; 23,8</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>133,47%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>109,49%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 29,79</t>
+          <t>-15,52; 31,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 53,13</t>
+          <t>-1,9; 50,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49,15; 116,2</t>
+          <t>45,26; 106,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,44; 52,82</t>
+          <t>4,23; 54,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,97; 68,4</t>
+          <t>11,02; 61,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>72,8; 257,56</t>
+          <t>51,99; 114,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 32,56</t>
+          <t>-0,24; 34,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>11,19; 47,92</t>
+          <t>11,22; 47,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>71,98; 188,83</t>
+          <t>57,01; 100,48</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16,17</t>
+          <t>32,95</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,81</t>
+          <t>34,96</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>23,94</t>
+          <t>33,92</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,64; 17,6</t>
+          <t>6,09; 17,88</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17,59; 28,38</t>
+          <t>17,21; 28,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 34,79</t>
+          <t>27,28; 38,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 9,23</t>
+          <t>-1,68; 9,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,23; 23,33</t>
+          <t>11,99; 23,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>30,15; 39,56</t>
+          <t>30,04; 39,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,54</t>
+          <t>3,74; 11,51</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>16,56; 24,52</t>
+          <t>16,54; 23,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,31; 35,15</t>
+          <t>30,47; 37,43</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>109,41%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>102,35%</t>
+          <t>102,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>105,4%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>20,2; 65,03</t>
+          <t>18,28; 66,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>53,04; 105,04</t>
+          <t>50,56; 104,38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 119,95</t>
+          <t>81,55; 143,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 29,14</t>
+          <t>-4,55; 29,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>33,4; 74,87</t>
+          <t>31,77; 76,84</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>81,12; 128,73</t>
+          <t>80,87; 130,55</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,89; 39,05</t>
+          <t>10,74; 37,73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>47,93; 82,65</t>
+          <t>48,38; 79,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10,19; 112,32</t>
+          <t>87,03; 124,58</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14,93</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,54</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>19,05</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,78</t>
+          <t>-1,63; 3,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,65</t>
+          <t>3,35; 8,8</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,34; 19,18</t>
+          <t>15,74; 21,04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,48</t>
+          <t>-0,52; 4,34</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,55</t>
+          <t>5,44; 10,47</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,82</t>
+          <t>17,29; 21,79</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,34</t>
+          <t>-0,07; 3,45</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,17</t>
+          <t>5,44; 9,08</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12,78; 22,28</t>
+          <t>17,19; 20,7</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 13,91</t>
+          <t>-5,43; 14,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11,37; 31,2</t>
+          <t>11,23; 32,68</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>19,64; 68,68</t>
+          <t>51,99; 77,5</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 16,04</t>
+          <t>-1,7; 15,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>17,51; 38,09</t>
+          <t>18,08; 37,38</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>55,69; 103,71</t>
+          <t>55,9; 78,71</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,05</t>
+          <t>-0,25; 12,28</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>18,32; 32,88</t>
+          <t>18,37; 32,8</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>43,93; 79,59</t>
+          <t>57,68; 74,06</t>
         </is>
       </c>
     </row>
